--- a/results/ACTUALRESULTS.xlsx
+++ b/results/ACTUALRESULTS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\audricho\Documents\ForOfficialDemo\Mutlithreading_Tester\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\audricho\Documents\ForOfficialDemo\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F9A8B6-2B1C-4CA5-A152-AB8159E4EB70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2657A02F-82E4-4438-ABD5-0070EF04B86B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{BFC95034-0712-4A02-8952-872159A7A178}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BFC95034-0712-4A02-8952-872159A7A178}"/>
   </bookViews>
   <sheets>
     <sheet name="SERVER-SERVER" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -3699,63 +3699,63 @@
         <v>15</v>
       </c>
       <c r="D56" s="2">
-        <f>AVERAGE(D2:D51)</f>
+        <f t="shared" ref="D56:R56" si="0">AVERAGE(D2:D51)</f>
         <v>150.94</v>
       </c>
       <c r="E56" s="3">
-        <f>AVERAGE(E2:E51)</f>
+        <f t="shared" si="0"/>
         <v>1257.3</v>
       </c>
       <c r="F56" s="4">
-        <f>AVERAGE(F2:F51)</f>
+        <f t="shared" si="0"/>
         <v>1159.8399999999999</v>
       </c>
       <c r="G56" s="5">
-        <f>AVERAGE(G2:G51)</f>
+        <f t="shared" si="0"/>
         <v>469.02</v>
       </c>
       <c r="H56" s="2">
-        <f>AVERAGE(H2:H51)</f>
+        <f t="shared" si="0"/>
         <v>251.92</v>
       </c>
       <c r="I56" s="2">
-        <f>AVERAGE(I2:I51)</f>
+        <f t="shared" si="0"/>
         <v>244.4</v>
       </c>
       <c r="J56" s="3">
-        <f>AVERAGE(J2:J51)</f>
+        <f t="shared" si="0"/>
         <v>2243.4</v>
       </c>
       <c r="K56" s="3">
-        <f>AVERAGE(K2:K51)</f>
+        <f t="shared" si="0"/>
         <v>2248.42</v>
       </c>
       <c r="L56" s="5">
-        <f>AVERAGE(L2:L51)</f>
+        <f t="shared" si="0"/>
         <v>872.36</v>
       </c>
       <c r="M56" s="5">
-        <f>AVERAGE(M2:M51)</f>
+        <f t="shared" si="0"/>
         <v>869.26</v>
       </c>
       <c r="N56" s="4">
-        <f>AVERAGE(N2:N51)</f>
+        <f t="shared" si="0"/>
         <v>1575.28</v>
       </c>
       <c r="O56" s="4">
-        <f>AVERAGE(O2:O51)</f>
+        <f t="shared" si="0"/>
         <v>1568.84</v>
       </c>
       <c r="P56" s="2">
-        <f>AVERAGE(P2:P51)</f>
+        <f t="shared" si="0"/>
         <v>294.18</v>
       </c>
       <c r="Q56" s="2">
-        <f>AVERAGE(Q2:Q51)</f>
+        <f t="shared" si="0"/>
         <v>265.82</v>
       </c>
       <c r="R56" s="3">
-        <f>AVERAGE(R2:R51)</f>
+        <f t="shared" si="0"/>
         <v>2056.3000000000002</v>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>3</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>0</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>1</v>
       </c>
@@ -4063,7 +4063,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>2</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>0</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>1</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>2</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>0</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>1</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>2</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>0</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>1</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>2</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>0</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>1</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>2</v>
       </c>
@@ -4199,7 +4199,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>0</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>1</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>2</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>0</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>1</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>2</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>3</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>0</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>1</v>
       </c>
@@ -4287,7 +4287,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>2</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>0</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>1</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>2</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>3</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>0</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>1</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>2</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>3</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>0</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>1</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>2</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>3</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>0</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>1</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>2</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>3</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>0</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>1</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>2</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>3</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>0</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>1</v>
       </c>
@@ -4479,7 +4479,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>2</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>3</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>0</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>1</v>
       </c>
@@ -4511,7 +4511,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>2</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>3</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>0</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>1</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>2</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>3</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>0</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>1</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>2</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>3</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>0</v>
       </c>
@@ -4599,7 +4599,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>1</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>2</v>
       </c>
@@ -4615,7 +4615,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>3</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>0</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>1</v>
       </c>
@@ -4639,7 +4639,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>2</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>3</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>0</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>1</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>2</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>3</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>0</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>1</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>2</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>3</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>0</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>1</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>2</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>3</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>0</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>1</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>2</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>3</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>0</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>1</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>2</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>3</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>0</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>1</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>2</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>3</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>0</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>1</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>2</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>3</v>
       </c>
@@ -4879,7 +4879,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>0</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>1</v>
       </c>
@@ -4895,7 +4895,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>2</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>3</v>
       </c>
@@ -4911,7 +4911,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>0</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>1</v>
       </c>
@@ -4927,7 +4927,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>2</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>3</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>0</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>1</v>
       </c>
@@ -4959,7 +4959,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>2</v>
       </c>
@@ -4967,7 +4967,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>3</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>0</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>1</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>2</v>
       </c>
@@ -4999,7 +4999,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>3</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>0</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>1</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>2</v>
       </c>
@@ -5031,7 +5031,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>3</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>0</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>1</v>
       </c>
@@ -5055,7 +5055,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>2</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>3</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>0</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>1</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>2</v>
       </c>
@@ -5095,7 +5095,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>3</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>0</v>
       </c>
@@ -5111,7 +5111,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>1</v>
       </c>
@@ -5119,7 +5119,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>2</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>3</v>
       </c>
@@ -5135,7 +5135,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>4</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>5</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>6</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>7</v>
       </c>
@@ -5167,7 +5167,7 @@
         <v>2227</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>8</v>
       </c>
@@ -5175,7 +5175,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>9</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>10</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>11</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>4</v>
       </c>
@@ -5207,7 +5207,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>5</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>6</v>
       </c>
@@ -5223,7 +5223,7 @@
         <v>2380</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>7</v>
       </c>
@@ -5231,7 +5231,7 @@
         <v>2535</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>8</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>9</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>10</v>
       </c>
@@ -5255,7 +5255,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>11</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>4</v>
       </c>
@@ -5271,7 +5271,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>5</v>
       </c>
@@ -5279,7 +5279,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>6</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>7</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>8</v>
       </c>
@@ -5303,7 +5303,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>9</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>10</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>11</v>
       </c>
@@ -5327,7 +5327,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>4</v>
       </c>
@@ -5335,7 +5335,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>5</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>6</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>2230</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>7</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>8</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>9</v>
       </c>
@@ -5375,7 +5375,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>10</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>11</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>4</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>5</v>
       </c>
@@ -5407,7 +5407,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>6</v>
       </c>
@@ -5415,7 +5415,7 @@
         <v>2270</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>7</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>8</v>
       </c>
@@ -5431,7 +5431,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>9</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>10</v>
       </c>
@@ -5447,7 +5447,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>11</v>
       </c>
@@ -5455,7 +5455,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>4</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>5</v>
       </c>
@@ -5471,7 +5471,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>6</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>7</v>
       </c>
@@ -5487,7 +5487,7 @@
         <v>2221</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>8</v>
       </c>
@@ -5495,7 +5495,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>9</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>10</v>
       </c>
@@ -5511,7 +5511,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>11</v>
       </c>
@@ -5519,7 +5519,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>4</v>
       </c>
@@ -5527,7 +5527,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>5</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>6</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>7</v>
       </c>
@@ -5551,7 +5551,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>8</v>
       </c>
@@ -5559,7 +5559,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>9</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>10</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>11</v>
       </c>
@@ -5583,7 +5583,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>4</v>
       </c>
@@ -5591,7 +5591,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>5</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>6</v>
       </c>
@@ -5607,7 +5607,7 @@
         <v>2336</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>7</v>
       </c>
@@ -5615,7 +5615,7 @@
         <v>2409</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>8</v>
       </c>
@@ -5623,7 +5623,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>9</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>10</v>
       </c>
@@ -5639,7 +5639,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>11</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>4</v>
       </c>
@@ -5655,7 +5655,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>5</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>6</v>
       </c>
@@ -5671,7 +5671,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>7</v>
       </c>
@@ -5679,7 +5679,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>8</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>9</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>10</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>11</v>
       </c>
@@ -5711,7 +5711,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>4</v>
       </c>
@@ -5719,7 +5719,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>5</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>6</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>7</v>
       </c>
@@ -5743,7 +5743,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>8</v>
       </c>
@@ -5751,7 +5751,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>9</v>
       </c>
@@ -5759,7 +5759,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>10</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>11</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>4</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>5</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>6</v>
       </c>
@@ -5799,7 +5799,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>7</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>8</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>9</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>10</v>
       </c>
@@ -5831,7 +5831,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>11</v>
       </c>
@@ -5839,7 +5839,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>4</v>
       </c>
@@ -5847,7 +5847,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>5</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>6</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>7</v>
       </c>
@@ -5871,7 +5871,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>8</v>
       </c>
@@ -5879,7 +5879,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>9</v>
       </c>
@@ -5887,7 +5887,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>10</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>11</v>
       </c>
@@ -5903,7 +5903,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>4</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>5</v>
       </c>
@@ -5919,7 +5919,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>6</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>7</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>8</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>9</v>
       </c>
@@ -5951,7 +5951,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>10</v>
       </c>
@@ -5959,7 +5959,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>11</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>4</v>
       </c>
@@ -5975,7 +5975,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>5</v>
       </c>
@@ -5983,7 +5983,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>6</v>
       </c>
@@ -5991,7 +5991,7 @@
         <v>2221</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>7</v>
       </c>
@@ -5999,7 +5999,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>8</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>9</v>
       </c>
@@ -6015,7 +6015,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>10</v>
       </c>
@@ -6023,7 +6023,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>11</v>
       </c>
@@ -6031,7 +6031,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>4</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>5</v>
       </c>
@@ -6047,7 +6047,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>6</v>
       </c>
@@ -6055,7 +6055,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>7</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>8</v>
       </c>
@@ -6071,7 +6071,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>9</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>10</v>
       </c>
@@ -6087,7 +6087,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>11</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>4</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>5</v>
       </c>
@@ -6111,7 +6111,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>6</v>
       </c>
@@ -6119,7 +6119,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>7</v>
       </c>
@@ -6127,7 +6127,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>8</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>9</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>10</v>
       </c>
@@ -6151,7 +6151,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>11</v>
       </c>
@@ -6159,7 +6159,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>4</v>
       </c>
@@ -6167,7 +6167,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>5</v>
       </c>
@@ -6175,7 +6175,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>6</v>
       </c>
@@ -6183,7 +6183,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>7</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>8</v>
       </c>
@@ -6199,7 +6199,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>9</v>
       </c>
@@ -6207,7 +6207,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>10</v>
       </c>
@@ -6215,7 +6215,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>11</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>4</v>
       </c>
@@ -6231,7 +6231,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>5</v>
       </c>
@@ -6239,7 +6239,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>6</v>
       </c>
@@ -6247,7 +6247,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>7</v>
       </c>
@@ -6255,7 +6255,7 @@
         <v>2230</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>8</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>9</v>
       </c>
@@ -6271,7 +6271,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>10</v>
       </c>
@@ -6279,7 +6279,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>11</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>4</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>5</v>
       </c>
@@ -6303,7 +6303,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>6</v>
       </c>
@@ -6311,7 +6311,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>7</v>
       </c>
@@ -6319,7 +6319,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>8</v>
       </c>
@@ -6327,7 +6327,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>9</v>
       </c>
@@ -6335,7 +6335,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>10</v>
       </c>
@@ -6343,7 +6343,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>11</v>
       </c>
@@ -6351,7 +6351,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>4</v>
       </c>
@@ -6359,7 +6359,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>5</v>
       </c>
@@ -6367,7 +6367,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>6</v>
       </c>
@@ -6375,7 +6375,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>7</v>
       </c>
@@ -6383,7 +6383,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>8</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>9</v>
       </c>
@@ -6399,7 +6399,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>10</v>
       </c>
@@ -6407,7 +6407,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>11</v>
       </c>
@@ -6415,7 +6415,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>4</v>
       </c>
@@ -6423,7 +6423,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>5</v>
       </c>
@@ -6431,7 +6431,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>6</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>7</v>
       </c>
@@ -6447,7 +6447,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>8</v>
       </c>
@@ -6455,7 +6455,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>9</v>
       </c>
@@ -6463,7 +6463,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>10</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>11</v>
       </c>
@@ -6479,7 +6479,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>4</v>
       </c>
@@ -6487,7 +6487,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
         <v>5</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>6</v>
       </c>
@@ -6503,7 +6503,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>7</v>
       </c>
@@ -6511,7 +6511,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>8</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>9</v>
       </c>
@@ -6527,7 +6527,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>10</v>
       </c>
@@ -6535,7 +6535,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>11</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>4</v>
       </c>
@@ -6551,7 +6551,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>5</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>6</v>
       </c>
@@ -6567,7 +6567,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>7</v>
       </c>
@@ -6575,7 +6575,7 @@
         <v>2422</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>8</v>
       </c>
@@ -6583,7 +6583,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>9</v>
       </c>
@@ -6591,7 +6591,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>10</v>
       </c>
@@ -6599,7 +6599,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>11</v>
       </c>
@@ -6607,7 +6607,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>4</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>5</v>
       </c>
@@ -6623,7 +6623,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>6</v>
       </c>
@@ -6631,7 +6631,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>7</v>
       </c>
@@ -6639,7 +6639,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>8</v>
       </c>
@@ -6647,7 +6647,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>9</v>
       </c>
@@ -6655,7 +6655,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>10</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>11</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>4</v>
       </c>
@@ -6679,7 +6679,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>5</v>
       </c>
@@ -6687,7 +6687,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>6</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>2194</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>7</v>
       </c>
@@ -6703,7 +6703,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>8</v>
       </c>
@@ -6711,7 +6711,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>9</v>
       </c>
@@ -6719,7 +6719,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>10</v>
       </c>
@@ -6727,7 +6727,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>11</v>
       </c>
@@ -6735,7 +6735,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>4</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>5</v>
       </c>
@@ -6751,7 +6751,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>6</v>
       </c>
@@ -6759,7 +6759,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>7</v>
       </c>
@@ -6767,7 +6767,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
         <v>8</v>
       </c>
@@ -6775,7 +6775,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
         <v>9</v>
       </c>
@@ -6783,7 +6783,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>10</v>
       </c>
@@ -6791,7 +6791,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>11</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>4</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>5</v>
       </c>
@@ -6815,7 +6815,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>6</v>
       </c>
@@ -6823,7 +6823,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>7</v>
       </c>
@@ -6831,7 +6831,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>8</v>
       </c>
@@ -6839,7 +6839,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>9</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>10</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>11</v>
       </c>
@@ -6863,7 +6863,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>4</v>
       </c>
@@ -6871,7 +6871,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>5</v>
       </c>
@@ -6879,7 +6879,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>6</v>
       </c>
@@ -6887,7 +6887,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>7</v>
       </c>
@@ -6895,7 +6895,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>8</v>
       </c>
@@ -6903,7 +6903,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>9</v>
       </c>
@@ -6911,7 +6911,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>10</v>
       </c>
@@ -6919,7 +6919,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>11</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>4</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
         <v>5</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
         <v>6</v>
       </c>
@@ -6951,7 +6951,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
         <v>7</v>
       </c>
@@ -6959,7 +6959,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
         <v>8</v>
       </c>
@@ -6967,7 +6967,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
         <v>9</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>10</v>
       </c>
@@ -6983,7 +6983,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
         <v>11</v>
       </c>
@@ -6991,7 +6991,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
         <v>4</v>
       </c>
@@ -6999,7 +6999,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
         <v>5</v>
       </c>
@@ -7007,7 +7007,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
         <v>6</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>2318</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
         <v>7</v>
       </c>
@@ -7023,7 +7023,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
         <v>8</v>
       </c>
@@ -7031,7 +7031,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
         <v>9</v>
       </c>
@@ -7039,7 +7039,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
         <v>10</v>
       </c>
@@ -7047,7 +7047,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
         <v>11</v>
       </c>
@@ -7055,7 +7055,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
         <v>4</v>
       </c>
@@ -7063,7 +7063,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
         <v>5</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
         <v>6</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
         <v>7</v>
       </c>
@@ -7087,7 +7087,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
         <v>8</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
         <v>9</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
         <v>10</v>
       </c>
@@ -7111,7 +7111,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
         <v>11</v>
       </c>
@@ -7119,7 +7119,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
         <v>4</v>
       </c>
@@ -7127,7 +7127,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>5</v>
       </c>
@@ -7135,7 +7135,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
         <v>6</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
         <v>7</v>
       </c>
@@ -7151,7 +7151,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
         <v>8</v>
       </c>
@@ -7159,7 +7159,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
         <v>9</v>
       </c>
@@ -7167,7 +7167,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
         <v>10</v>
       </c>
@@ -7175,7 +7175,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
         <v>11</v>
       </c>
@@ -7183,7 +7183,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
         <v>4</v>
       </c>
@@ -7191,7 +7191,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
         <v>5</v>
       </c>
@@ -7199,7 +7199,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
         <v>6</v>
       </c>
@@ -7207,7 +7207,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
         <v>7</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
         <v>8</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>9</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
         <v>10</v>
       </c>
@@ -7239,7 +7239,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
         <v>11</v>
       </c>
@@ -7247,7 +7247,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
         <v>4</v>
       </c>
@@ -7255,7 +7255,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
         <v>5</v>
       </c>
@@ -7263,7 +7263,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
         <v>6</v>
       </c>
@@ -7271,7 +7271,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
         <v>7</v>
       </c>
@@ -7279,7 +7279,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
         <v>8</v>
       </c>
@@ -7287,7 +7287,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
         <v>9</v>
       </c>
@@ -7295,7 +7295,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
         <v>10</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
         <v>11</v>
       </c>
@@ -7311,7 +7311,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
         <v>4</v>
       </c>
@@ -7319,7 +7319,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
         <v>5</v>
       </c>
@@ -7327,7 +7327,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
         <v>6</v>
       </c>
@@ -7335,7 +7335,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
         <v>7</v>
       </c>
@@ -7343,7 +7343,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
         <v>8</v>
       </c>
@@ -7351,7 +7351,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
         <v>9</v>
       </c>
@@ -7359,7 +7359,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
         <v>10</v>
       </c>
@@ -7367,7 +7367,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
         <v>11</v>
       </c>
@@ -7375,7 +7375,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
         <v>4</v>
       </c>
@@ -7383,7 +7383,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
         <v>5</v>
       </c>
@@ -7391,7 +7391,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
         <v>6</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
         <v>7</v>
       </c>
@@ -7407,7 +7407,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
         <v>8</v>
       </c>
@@ -7415,7 +7415,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>9</v>
       </c>
@@ -7423,7 +7423,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
         <v>10</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
         <v>11</v>
       </c>
@@ -7439,7 +7439,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
         <v>4</v>
       </c>
@@ -7447,7 +7447,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
         <v>5</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
         <v>6</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>2353</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
         <v>7</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>2581</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
         <v>8</v>
       </c>
@@ -7479,7 +7479,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
         <v>9</v>
       </c>
@@ -7487,7 +7487,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
         <v>10</v>
       </c>
@@ -7495,7 +7495,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
         <v>11</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
         <v>4</v>
       </c>
@@ -7511,7 +7511,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
         <v>5</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
         <v>6</v>
       </c>
@@ -7527,7 +7527,7 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
         <v>7</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>2198</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
         <v>8</v>
       </c>
@@ -7543,7 +7543,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
         <v>9</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>10</v>
       </c>
@@ -7559,7 +7559,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
         <v>11</v>
       </c>
@@ -7567,7 +7567,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
         <v>4</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
         <v>5</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
         <v>6</v>
       </c>
@@ -7591,7 +7591,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
         <v>7</v>
       </c>
@@ -7599,7 +7599,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
         <v>8</v>
       </c>
@@ -7607,7 +7607,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
         <v>9</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
         <v>10</v>
       </c>
@@ -7623,7 +7623,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
         <v>11</v>
       </c>
@@ -7631,7 +7631,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
         <v>4</v>
       </c>
@@ -7639,7 +7639,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
         <v>5</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
         <v>6</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
         <v>7</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
         <v>8</v>
       </c>
@@ -7671,7 +7671,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
         <v>9</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
         <v>10</v>
       </c>
@@ -7687,7 +7687,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
         <v>11</v>
       </c>
@@ -7695,7 +7695,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
         <v>4</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
         <v>5</v>
       </c>
@@ -7711,7 +7711,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="s">
         <v>6</v>
       </c>
@@ -7719,7 +7719,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
         <v>7</v>
       </c>
@@ -7727,7 +7727,7 @@
         <v>2194</v>
       </c>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="s">
         <v>8</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
         <v>9</v>
       </c>
@@ -7743,7 +7743,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A537" s="1" t="s">
         <v>10</v>
       </c>
@@ -7751,7 +7751,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
         <v>11</v>
       </c>
@@ -7759,7 +7759,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A539" s="1" t="s">
         <v>4</v>
       </c>
@@ -7767,7 +7767,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
         <v>5</v>
       </c>
@@ -7775,7 +7775,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A541" s="1" t="s">
         <v>6</v>
       </c>
@@ -7783,7 +7783,7 @@
         <v>2198</v>
       </c>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
         <v>7</v>
       </c>
@@ -7791,7 +7791,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A543" s="1" t="s">
         <v>8</v>
       </c>
@@ -7799,7 +7799,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
         <v>9</v>
       </c>
@@ -7807,7 +7807,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="s">
         <v>10</v>
       </c>
@@ -7815,7 +7815,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
         <v>11</v>
       </c>
@@ -7823,7 +7823,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A547" s="1" t="s">
         <v>4</v>
       </c>
@@ -7831,7 +7831,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
         <v>5</v>
       </c>
@@ -7839,7 +7839,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A549" s="1" t="s">
         <v>6</v>
       </c>
@@ -7847,7 +7847,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
         <v>7</v>
       </c>
@@ -7855,7 +7855,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A551" s="1" t="s">
         <v>8</v>
       </c>
@@ -7863,7 +7863,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
         <v>9</v>
       </c>
@@ -7871,7 +7871,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A553" s="1" t="s">
         <v>10</v>
       </c>
@@ -7879,7 +7879,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
         <v>11</v>
       </c>
@@ -7887,7 +7887,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A555" s="1" t="s">
         <v>4</v>
       </c>
@@ -7895,7 +7895,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
         <v>5</v>
       </c>
@@ -7903,7 +7903,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A557" s="1" t="s">
         <v>6</v>
       </c>
@@ -7911,7 +7911,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
         <v>7</v>
       </c>
@@ -7919,7 +7919,7 @@
         <v>2362</v>
       </c>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A559" s="1" t="s">
         <v>8</v>
       </c>
@@ -7927,7 +7927,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
         <v>9</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A561" s="1" t="s">
         <v>10</v>
       </c>
@@ -7943,7 +7943,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
         <v>11</v>
       </c>
@@ -7951,7 +7951,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A563" s="1" t="s">
         <v>4</v>
       </c>
@@ -7959,7 +7959,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
         <v>5</v>
       </c>
@@ -7967,7 +7967,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A565" s="1" t="s">
         <v>6</v>
       </c>
@@ -7975,7 +7975,7 @@
         <v>2297</v>
       </c>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
         <v>7</v>
       </c>
@@ -7983,7 +7983,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A567" s="1" t="s">
         <v>8</v>
       </c>
@@ -7991,7 +7991,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
         <v>9</v>
       </c>
@@ -7999,7 +7999,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A569" s="1" t="s">
         <v>10</v>
       </c>
@@ -8007,7 +8007,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
         <v>11</v>
       </c>
@@ -8015,7 +8015,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A571" s="1" t="s">
         <v>4</v>
       </c>
@@ -8023,7 +8023,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
         <v>5</v>
       </c>
@@ -8031,7 +8031,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="s">
         <v>6</v>
       </c>
@@ -8039,7 +8039,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
         <v>7</v>
       </c>
@@ -8047,7 +8047,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A575" s="1" t="s">
         <v>8</v>
       </c>
@@ -8055,7 +8055,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
         <v>9</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A577" s="1" t="s">
         <v>10</v>
       </c>
@@ -8071,7 +8071,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
         <v>11</v>
       </c>
@@ -8079,7 +8079,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A579" s="1" t="s">
         <v>4</v>
       </c>
@@ -8087,7 +8087,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
         <v>5</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A581" s="1" t="s">
         <v>6</v>
       </c>
@@ -8103,7 +8103,7 @@
         <v>2221</v>
       </c>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
         <v>7</v>
       </c>
@@ -8111,7 +8111,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A583" s="1" t="s">
         <v>8</v>
       </c>
@@ -8119,7 +8119,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
         <v>9</v>
       </c>
@@ -8127,7 +8127,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A585" s="1" t="s">
         <v>10</v>
       </c>
@@ -8135,7 +8135,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
         <v>11</v>
       </c>
@@ -8143,7 +8143,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A587" s="1" t="s">
         <v>4</v>
       </c>
@@ -8151,7 +8151,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
         <v>5</v>
       </c>
@@ -8159,7 +8159,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A589" s="1" t="s">
         <v>6</v>
       </c>
@@ -8167,7 +8167,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
         <v>7</v>
       </c>
@@ -8175,7 +8175,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A591" s="1" t="s">
         <v>8</v>
       </c>
@@ -8183,7 +8183,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
         <v>9</v>
       </c>
@@ -8191,7 +8191,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A593" s="1" t="s">
         <v>10</v>
       </c>
@@ -8199,7 +8199,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
         <v>11</v>
       </c>
@@ -8207,7 +8207,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A595" s="1" t="s">
         <v>4</v>
       </c>
@@ -8215,7 +8215,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
         <v>5</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A597" s="1" t="s">
         <v>6</v>
       </c>
@@ -8231,7 +8231,7 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
         <v>7</v>
       </c>
@@ -8239,7 +8239,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A599" s="1" t="s">
         <v>8</v>
       </c>
@@ -8247,7 +8247,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="s">
         <v>9</v>
       </c>
@@ -8255,7 +8255,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A601" s="1" t="s">
         <v>10</v>
       </c>
@@ -8263,7 +8263,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
         <v>11</v>
       </c>
@@ -8271,7 +8271,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A603" s="1" t="s">
         <v>4</v>
       </c>
@@ -8279,7 +8279,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
         <v>5</v>
       </c>
@@ -8287,7 +8287,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A605" s="1" t="s">
         <v>6</v>
       </c>
@@ -8295,7 +8295,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
         <v>7</v>
       </c>
@@ -8303,7 +8303,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A607" s="1" t="s">
         <v>8</v>
       </c>
@@ -8311,7 +8311,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="s">
         <v>9</v>
       </c>
@@ -8319,7 +8319,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A609" s="1" t="s">
         <v>10</v>
       </c>
@@ -8327,7 +8327,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="s">
         <v>11</v>
       </c>
@@ -8335,7 +8335,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A621" s="1" t="s">
         <v>12</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A622" s="1" t="s">
         <v>13</v>
       </c>
@@ -8351,7 +8351,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A623" s="1" t="s">
         <v>14</v>
       </c>
@@ -8359,7 +8359,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="s">
         <v>12</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A625" s="1" t="s">
         <v>13</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A626" s="1" t="s">
         <v>14</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>2230</v>
       </c>
     </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A627" s="1" t="s">
         <v>12</v>
       </c>
@@ -8391,7 +8391,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A628" s="1" t="s">
         <v>13</v>
       </c>
@@ -8399,7 +8399,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A629" s="1" t="s">
         <v>14</v>
       </c>
@@ -8407,7 +8407,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A630" s="1" t="s">
         <v>12</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="631" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A631" s="1" t="s">
         <v>13</v>
       </c>
@@ -8423,7 +8423,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="632" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A632" s="1" t="s">
         <v>14</v>
       </c>
@@ -8431,7 +8431,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="633" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A633" s="1" t="s">
         <v>12</v>
       </c>
@@ -8439,7 +8439,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="634" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
         <v>13</v>
       </c>
@@ -8447,7 +8447,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="635" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A635" s="1" t="s">
         <v>14</v>
       </c>
@@ -8455,7 +8455,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="636" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A636" s="1" t="s">
         <v>12</v>
       </c>
@@ -8463,7 +8463,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="637" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A637" s="1" t="s">
         <v>13</v>
       </c>
@@ -8471,7 +8471,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A638" s="1" t="s">
         <v>14</v>
       </c>
@@ -8479,7 +8479,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="639" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A639" s="1" t="s">
         <v>12</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A640" s="1" t="s">
         <v>13</v>
       </c>
@@ -8495,7 +8495,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A641" s="1" t="s">
         <v>14</v>
       </c>
@@ -8503,7 +8503,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A642" s="1" t="s">
         <v>12</v>
       </c>
@@ -8511,7 +8511,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A643" s="1" t="s">
         <v>13</v>
       </c>
@@ -8519,7 +8519,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A644" s="1" t="s">
         <v>14</v>
       </c>
@@ -8527,7 +8527,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A645" s="1" t="s">
         <v>12</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A646" s="1" t="s">
         <v>13</v>
       </c>
@@ -8543,7 +8543,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A647" s="1" t="s">
         <v>14</v>
       </c>
@@ -8551,7 +8551,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A648" s="1" t="s">
         <v>12</v>
       </c>
@@ -8559,7 +8559,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A649" s="1" t="s">
         <v>13</v>
       </c>
@@ -8567,7 +8567,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A650" s="1" t="s">
         <v>14</v>
       </c>
@@ -8575,7 +8575,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A651" s="1" t="s">
         <v>12</v>
       </c>
@@ -8583,7 +8583,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A652" s="1" t="s">
         <v>13</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A653" s="1" t="s">
         <v>14</v>
       </c>
@@ -8599,7 +8599,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A654" s="1" t="s">
         <v>12</v>
       </c>
@@ -8607,7 +8607,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A655" s="1" t="s">
         <v>13</v>
       </c>
@@ -8615,7 +8615,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A656" s="1" t="s">
         <v>14</v>
       </c>
@@ -8623,7 +8623,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="657" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A657" s="1" t="s">
         <v>12</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="658" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A658" s="1" t="s">
         <v>13</v>
       </c>
@@ -8639,7 +8639,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A659" s="1" t="s">
         <v>14</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A660" s="1" t="s">
         <v>12</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="661" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A661" s="1" t="s">
         <v>13</v>
       </c>
@@ -8663,7 +8663,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="662" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A662" s="1" t="s">
         <v>14</v>
       </c>
@@ -8671,7 +8671,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A663" s="1" t="s">
         <v>12</v>
       </c>
@@ -8679,7 +8679,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A664" s="1" t="s">
         <v>13</v>
       </c>
@@ -8687,7 +8687,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A665" s="1" t="s">
         <v>14</v>
       </c>
@@ -8695,7 +8695,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="666" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A666" s="1" t="s">
         <v>12</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="667" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A667" s="1" t="s">
         <v>13</v>
       </c>
@@ -8711,7 +8711,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="668" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A668" s="1" t="s">
         <v>14</v>
       </c>
@@ -8719,7 +8719,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="669" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A669" s="1" t="s">
         <v>12</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="670" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A670" s="1" t="s">
         <v>13</v>
       </c>
@@ -8735,7 +8735,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A671" s="1" t="s">
         <v>14</v>
       </c>
@@ -8743,7 +8743,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A672" s="1" t="s">
         <v>12</v>
       </c>
@@ -8751,7 +8751,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A673" s="1" t="s">
         <v>13</v>
       </c>
@@ -8759,7 +8759,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A674" s="1" t="s">
         <v>14</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A675" s="1" t="s">
         <v>12</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A676" s="1" t="s">
         <v>13</v>
       </c>
@@ -8783,7 +8783,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A677" s="1" t="s">
         <v>14</v>
       </c>
@@ -8791,7 +8791,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A678" s="1" t="s">
         <v>12</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A679" s="1" t="s">
         <v>13</v>
       </c>
@@ -8807,7 +8807,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A680" s="1" t="s">
         <v>14</v>
       </c>
@@ -8815,7 +8815,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A681" s="1" t="s">
         <v>12</v>
       </c>
@@ -8823,7 +8823,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A682" s="1" t="s">
         <v>13</v>
       </c>
@@ -8831,7 +8831,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A683" s="1" t="s">
         <v>14</v>
       </c>
@@ -8839,7 +8839,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A684" s="1" t="s">
         <v>12</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A685" s="1" t="s">
         <v>13</v>
       </c>
@@ -8855,7 +8855,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A686" s="1" t="s">
         <v>14</v>
       </c>
@@ -8863,7 +8863,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A687" s="1" t="s">
         <v>12</v>
       </c>
@@ -8871,7 +8871,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A688" s="1" t="s">
         <v>13</v>
       </c>
@@ -8879,7 +8879,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A689" s="1" t="s">
         <v>14</v>
       </c>
@@ -8887,7 +8887,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A690" s="1" t="s">
         <v>12</v>
       </c>
@@ -8895,7 +8895,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A691" s="1" t="s">
         <v>13</v>
       </c>
@@ -8903,7 +8903,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="692" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A692" s="1" t="s">
         <v>14</v>
       </c>
@@ -8911,7 +8911,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="693" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A693" s="1" t="s">
         <v>12</v>
       </c>
@@ -8919,7 +8919,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="694" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A694" s="1" t="s">
         <v>13</v>
       </c>
@@ -8927,7 +8927,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="695" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A695" s="1" t="s">
         <v>14</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="696" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A696" s="1" t="s">
         <v>12</v>
       </c>
@@ -8943,7 +8943,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="697" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A697" s="1" t="s">
         <v>13</v>
       </c>
@@ -8951,7 +8951,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="698" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A698" s="1" t="s">
         <v>14</v>
       </c>
@@ -8959,7 +8959,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="699" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A699" s="1" t="s">
         <v>12</v>
       </c>
@@ -8967,7 +8967,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="700" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A700" s="1" t="s">
         <v>13</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="701" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A701" s="1" t="s">
         <v>14</v>
       </c>
@@ -8983,7 +8983,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="702" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A702" s="1" t="s">
         <v>12</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="703" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A703" s="1" t="s">
         <v>13</v>
       </c>
@@ -8999,7 +8999,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="704" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A704" s="1" t="s">
         <v>14</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A705" s="1" t="s">
         <v>12</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="706" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A706" s="1" t="s">
         <v>13</v>
       </c>
@@ -9023,7 +9023,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="707" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A707" s="1" t="s">
         <v>14</v>
       </c>
@@ -9031,7 +9031,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="708" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A708" s="1" t="s">
         <v>12</v>
       </c>
@@ -9039,7 +9039,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="709" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A709" s="1" t="s">
         <v>13</v>
       </c>
@@ -9047,7 +9047,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="710" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A710" s="1" t="s">
         <v>14</v>
       </c>
@@ -9055,7 +9055,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="711" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A711" s="1" t="s">
         <v>12</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="712" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A712" s="1" t="s">
         <v>13</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="713" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A713" s="1" t="s">
         <v>14</v>
       </c>
@@ -9079,7 +9079,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="714" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A714" s="1" t="s">
         <v>12</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="715" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A715" s="1" t="s">
         <v>13</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="716" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A716" s="1" t="s">
         <v>14</v>
       </c>
@@ -9103,7 +9103,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="717" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A717" s="1" t="s">
         <v>12</v>
       </c>
@@ -9111,7 +9111,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="718" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A718" s="1" t="s">
         <v>13</v>
       </c>
@@ -9119,7 +9119,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="719" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A719" s="1" t="s">
         <v>14</v>
       </c>
@@ -9127,7 +9127,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="720" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A720" s="1" t="s">
         <v>12</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="721" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A721" s="1" t="s">
         <v>13</v>
       </c>
@@ -9143,7 +9143,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="722" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A722" s="1" t="s">
         <v>14</v>
       </c>
@@ -9151,7 +9151,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="723" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A723" s="1" t="s">
         <v>12</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="724" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A724" s="1" t="s">
         <v>13</v>
       </c>
@@ -9167,7 +9167,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="725" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A725" s="1" t="s">
         <v>14</v>
       </c>
@@ -9175,7 +9175,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="726" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A726" s="1" t="s">
         <v>12</v>
       </c>
@@ -9183,7 +9183,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="727" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A727" s="1" t="s">
         <v>13</v>
       </c>
@@ -9191,7 +9191,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="728" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A728" s="1" t="s">
         <v>14</v>
       </c>
@@ -9199,7 +9199,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A729" s="1" t="s">
         <v>12</v>
       </c>
@@ -9207,7 +9207,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="730" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A730" s="1" t="s">
         <v>13</v>
       </c>
@@ -9215,7 +9215,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="731" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A731" s="1" t="s">
         <v>14</v>
       </c>
@@ -9223,7 +9223,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="732" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A732" s="1" t="s">
         <v>12</v>
       </c>
@@ -9231,7 +9231,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="733" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A733" s="1" t="s">
         <v>13</v>
       </c>
@@ -9239,7 +9239,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="734" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A734" s="1" t="s">
         <v>14</v>
       </c>
@@ -9247,7 +9247,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="735" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A735" s="1" t="s">
         <v>12</v>
       </c>
@@ -9255,7 +9255,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="736" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A736" s="1" t="s">
         <v>13</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="737" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A737" s="1" t="s">
         <v>14</v>
       </c>
@@ -9271,7 +9271,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="738" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A738" s="1" t="s">
         <v>12</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="739" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A739" s="1" t="s">
         <v>13</v>
       </c>
@@ -9287,7 +9287,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="740" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A740" s="1" t="s">
         <v>14</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="741" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A741" s="1" t="s">
         <v>12</v>
       </c>
@@ -9303,7 +9303,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="742" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A742" s="1" t="s">
         <v>13</v>
       </c>
@@ -9311,7 +9311,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="743" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A743" s="1" t="s">
         <v>14</v>
       </c>
@@ -9319,7 +9319,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="744" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A744" s="1" t="s">
         <v>12</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="745" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A745" s="1" t="s">
         <v>13</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="746" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A746" s="1" t="s">
         <v>14</v>
       </c>
@@ -9343,7 +9343,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="747" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A747" s="1" t="s">
         <v>12</v>
       </c>
@@ -9351,7 +9351,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="748" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A748" s="1" t="s">
         <v>13</v>
       </c>
@@ -9359,7 +9359,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="749" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A749" s="1" t="s">
         <v>14</v>
       </c>
@@ -9367,7 +9367,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="750" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A750" s="1" t="s">
         <v>12</v>
       </c>
@@ -9375,7 +9375,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="751" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A751" s="1" t="s">
         <v>13</v>
       </c>
@@ -9383,7 +9383,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="752" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A752" s="1" t="s">
         <v>14</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="753" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A753" s="1" t="s">
         <v>12</v>
       </c>
@@ -9399,7 +9399,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="754" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A754" s="1" t="s">
         <v>13</v>
       </c>
@@ -9407,7 +9407,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="755" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A755" s="1" t="s">
         <v>14</v>
       </c>
@@ -9415,7 +9415,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="756" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A756" s="1" t="s">
         <v>12</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="757" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A757" s="1" t="s">
         <v>13</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="758" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A758" s="1" t="s">
         <v>14</v>
       </c>
@@ -9439,7 +9439,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="759" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A759" s="1" t="s">
         <v>12</v>
       </c>
@@ -9447,7 +9447,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="760" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A760" s="1" t="s">
         <v>13</v>
       </c>
@@ -9455,7 +9455,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="761" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A761" s="1" t="s">
         <v>14</v>
       </c>
@@ -9463,7 +9463,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="762" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A762" s="1" t="s">
         <v>12</v>
       </c>
@@ -9471,7 +9471,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="763" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A763" s="1" t="s">
         <v>13</v>
       </c>
@@ -9479,7 +9479,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="764" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A764" s="1" t="s">
         <v>14</v>
       </c>
@@ -9487,7 +9487,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="765" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A765" s="1" t="s">
         <v>12</v>
       </c>
@@ -9495,7 +9495,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="766" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A766" s="1" t="s">
         <v>13</v>
       </c>
@@ -9503,7 +9503,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="767" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A767" s="1" t="s">
         <v>14</v>
       </c>
@@ -9511,7 +9511,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="768" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A768" s="1" t="s">
         <v>12</v>
       </c>
@@ -9519,7 +9519,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="769" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A769" s="1" t="s">
         <v>13</v>
       </c>
@@ -9527,7 +9527,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="770" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A770" s="1" t="s">
         <v>14</v>
       </c>

--- a/results/ACTUALRESULTS.xlsx
+++ b/results/ACTUALRESULTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\audricho\Documents\ForOfficialDemo\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2657A02F-82E4-4438-ABD5-0070EF04B86B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73578C2C-3435-431D-98B3-EF6D6C37A451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BFC95034-0712-4A02-8952-872159A7A178}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="80">
   <si>
     <t>stubGRPCPeoplePeopleInfoServiceStub P-R</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>(Lower Better)</t>
+  </si>
+  <si>
+    <t>Protocol / Architecture Type</t>
   </si>
 </sst>
 </file>
@@ -791,8 +794,8 @@
   <sheetFormatPr defaultColWidth="7.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="7.77734375" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="7.77734375" style="1" customWidth="1"/>
-    <col min="4" max="18" width="13.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" style="1" customWidth="1"/>
+    <col min="4" max="18" width="13.77734375" style="1" customWidth="1"/>
     <col min="19" max="16384" width="7.77734375" style="1"/>
   </cols>
   <sheetData>
@@ -3523,7 +3526,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>0</v>
       </c>
@@ -3531,7 +3534,7 @@
         <v>212</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>16</v>
@@ -3688,7 +3691,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>3</v>
       </c>
@@ -3820,7 +3823,7 @@
         <v>2056.3000000000002</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>2</v>
       </c>
@@ -3891,7 +3894,7 @@
         <v>0.61143801974420064</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>3</v>
       </c>
@@ -9563,7 +9566,7 @@
     <col min="15" max="15" width="16.77734375" customWidth="1"/>
     <col min="16" max="16" width="15.6640625" customWidth="1"/>
     <col min="26" max="26" width="8.88671875" customWidth="1"/>
-    <col min="27" max="27" width="7.77734375" customWidth="1"/>
+    <col min="27" max="27" width="11.33203125" customWidth="1"/>
     <col min="28" max="42" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9964,9 +9967,9 @@
       <c r="AO20" s="1"/>
       <c r="AP20" s="1"/>
     </row>
-    <row r="21" spans="27:42" x14ac:dyDescent="0.3">
+    <row r="21" spans="27:42" ht="72" x14ac:dyDescent="0.3">
       <c r="AA21" s="1" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="AB21" s="1" t="s">
         <v>16</v>
